--- a/港岛-筲箕湾-远晴/远晴_销控明细表.xlsx
+++ b/港岛-筲箕湾-远晴/远晴_销控明细表.xlsx
@@ -5447,7 +5447,7 @@
           <t>A | 434呎 (1房)
 $782万
 $18,028/呎
-(14年-09月)</t>
+(14年-09月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5455,7 +5455,7 @@
           <t>B | 271呎 (1房)
 $555万
 $20,469/呎
-(14年-10月)</t>
+(14年-10月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -5463,7 +5463,7 @@
           <t>C | 276呎 (1房)
 $568万
 $20,598/呎
-(14年-09月)</t>
+(14年-09月-21日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -5486,7 +5486,7 @@
           <t>A | 434呎 (1房)
 $780万
 $17,984/呎
-(14年-09月)</t>
+(14年-09月-18日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5494,7 +5494,7 @@
           <t>B | 271呎 (1房)
 $553万
 $20,417/呎
-(14年-09月)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -5502,7 +5502,7 @@
           <t>C | 276呎 (1房)
 $567万
 $20,543/呎
-(14年-09月)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -5525,7 +5525,7 @@
           <t>A | 434呎 (1房)
 $746万
 $17,189/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5533,7 +5533,7 @@
           <t>B | 271呎 (1房)
 $542万
 $20,011/呎
-(14年-10月)</t>
+(14年-10月-02日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -5541,7 +5541,7 @@
           <t>C | 276呎 (1房)
 $556万
 $20,141/呎
-(14年-10月)</t>
+(14年-10月-02日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -5564,7 +5564,7 @@
           <t>A | 434呎 (1房)
 $742万
 $17,099/呎
-(14年-12月)</t>
+(14年-12月-09日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -5572,7 +5572,7 @@
           <t>B | 271呎 (1房)
 $537万
 $19,812/呎
-(14年-09月)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -5580,7 +5580,7 @@
           <t>C | 275呎 (1房)
 $550万
 $20,011/呎
-(14年-10月)</t>
+(14年-10月-07日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -5611,7 +5611,7 @@
           <t>B | 274呎 (1房)
 $532万
 $19,401/呎
-(14年-09月)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -5619,7 +5619,7 @@
           <t>C | 276呎 (1房)
 $545万
 $19,739/呎
-(14年-10月)</t>
+(14年-10月-05日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5642,7 +5642,7 @@
           <t>A | 431呎 (1房)
 $723万
 $16,773/呎
-(14年-12月)</t>
+(14年-12月-17日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5650,7 +5650,7 @@
           <t>B | 274呎 (1房)
 $529万
 $19,321/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -5658,7 +5658,7 @@
           <t>C | 276呎 (1房)
 $537万
 $19,446/呎
-(14年-08月)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -5681,7 +5681,7 @@
           <t>A | 431呎 (1房)
 $716万
 $16,608/呎
-(14年-10月)</t>
+(14年-10月-21日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5689,7 +5689,7 @@
           <t>B | 274呎 (1房)
 $524万
 $19,128/呎
-(14年-08月)</t>
+(14年-08月-09日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -5697,7 +5697,7 @@
           <t>C | 275呎 (1房)
 $531万
 $19,320/呎
-(14年-08月)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5720,7 +5720,7 @@
           <t>A | 431呎 (1房)
 $709万
 $16,443/呎
-(14年-10月)</t>
+(14年-10月-02日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5728,7 +5728,7 @@
           <t>B | 274呎 (1房)
 $519万
 $18,938/呎
-(14年-09月)</t>
+(14年-09月-03日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5736,7 +5736,7 @@
           <t>C | 276呎 (1房)
 $526万
 $19,062/呎
-(14年-09月)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -5759,7 +5759,7 @@
           <t>A | 431呎 (1房)
 $701万
 $16,271/呎
-(14年-10月)</t>
+(14年-10月-26日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5767,7 +5767,7 @@
           <t>B | 274呎 (1房)
 $514万
 $18,752/呎
-(14年-08月)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5775,7 +5775,7 @@
           <t>C | 276呎 (1房)
 $521万
 $18,870/呎
-(14年-08月)</t>
+(14年-08月-25日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -5798,7 +5798,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(14年-08月)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5806,7 +5806,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(14年-08月)</t>
+(14年-08月-24日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5814,7 +5814,7 @@
           <t>C | 276呎 (1房)
 $490万
 $17,768/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -5837,7 +5837,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5845,7 +5845,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(14年-08月)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5853,7 +5853,7 @@
           <t>C | 276呎 (1房)
 $490万
 $17,768/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -5876,7 +5876,7 @@
           <t>A | 431呎 (1房)
 $667万
 $15,485/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5884,7 +5884,7 @@
           <t>B | 274呎 (1房)
 $484万
 $17,653/呎
-(14年-08月)</t>
+(14年-08月-24日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5892,7 +5892,7 @@
           <t>C | 275呎 (1房)
 $486万
 $17,655/呎
-(14年-08月)</t>
+(14年-08月-18日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -5915,7 +5915,7 @@
           <t>A | 431呎 (1房)
 $650万
 $15,072/呎
-(14年-09月)</t>
+(14年-09月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5923,7 +5923,7 @@
           <t>B | 274呎 (1房)
 $481万
 $17,566/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5931,7 +5931,7 @@
           <t>C | 276呎 (1房)
 $483万
 $17,504/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -5954,7 +5954,7 @@
           <t>A | 431呎 (1房)
 $661万
 $15,334/呎
-(14年-09月)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5962,7 +5962,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,478/呎
-(14年-08月)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5970,7 +5970,7 @@
           <t>C | 276呎 (1房)
 $481万
 $17,417/呎
-(14年-08月)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -5993,7 +5993,7 @@
           <t>A | 431呎 (1房)
 $658万
 $15,255/呎
-(14年-08月)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -6001,7 +6001,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,394/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -6009,7 +6009,7 @@
           <t>C | 276呎 (1房)
 $478万
 $17,330/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -6032,7 +6032,7 @@
           <t>A | 431呎 (1房)
 $654万
 $15,179/呎
-(14年-09月)</t>
+(14年-09月-09日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -6040,7 +6040,7 @@
           <t>B | 274呎 (1房)
 $474万
 $17,307/呎
-(14年-08月)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -6048,7 +6048,7 @@
           <t>C | 276呎 (1房)
 $476万
 $17,243/呎
-(14年-08月)</t>
+(14年-08月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -6071,7 +6071,7 @@
           <t>A | 431呎 (1房)
 $651万
 $15,104/呎
-(14年-08月)</t>
+(14年-08月-18日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -6079,7 +6079,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,493/呎
-(14年-08月)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -6087,7 +6087,7 @@
           <t>C | 276呎 (1房)
 $486万
 $17,605/呎
-(14年-08月)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -6110,7 +6110,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -6118,7 +6118,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,409/呎
-(14年-08月)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -6126,7 +6126,7 @@
           <t>C | 276呎 (1房)
 $484万
 $17,518/呎
-(14年-09月)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -6149,7 +6149,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(14年-08月)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -6157,7 +6157,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,847/呎
-(14年-09月)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -6165,7 +6165,7 @@
           <t>C | 276呎 (1房)
 $496万
 $17,964/呎
-(14年-09月)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -6188,7 +6188,7 @@
           <t>A | 431呎 (1房)
 $641万
 $14,882/呎
-(14年-08月)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -6196,7 +6196,7 @@
           <t>B | 274呎 (1房)
 $472万
 $17,234/呎
-(14年-08月)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -6204,7 +6204,7 @@
           <t>C | 276呎 (1房)
 $479万
 $17,344/呎
-(14年-08月)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -6227,7 +6227,7 @@
           <t>A | 431呎 (1房)
 $629万
 $14,587/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -6235,7 +6235,7 @@
           <t>B | 274呎 (1房)
 $463万
 $16,894/呎
-(14年-08月)</t>
+(14年-08月-09日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -6243,7 +6243,7 @@
           <t>C | 276呎 (1房)
 $462万
 $16,757/呎
-(14年-08月)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -6266,7 +6266,7 @@
           <t>A | 431呎 (1房)
 $616万
 $14,302/呎
-(14年-09月)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -6274,7 +6274,7 @@
           <t>B | 274呎 (1房)
 $454万
 $16,562/呎
-(14年-09月)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -6282,7 +6282,7 @@
           <t>C | 276呎 (1房)
 $435万
 $15,775/呎
-(14年-08月)</t>
+(14年-08月-24日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -6313,7 +6313,7 @@
           <t>B | 253呎 (1房)
 $500万
 $19,751/呎
-(14年-09月)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6321,7 +6321,7 @@
           <t>C | 254呎 (1房)
 $462万
 $18,201/呎
-(14年-08月)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -6329,7 +6329,7 @@
           <t>D | 490呎 (2房)
 $812万
 $16,567/呎
-(14年-08月)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
     </row>

--- a/港岛-筲箕湾-远晴/远晴_销控明细表.xlsx
+++ b/港岛-筲箕湾-远晴/远晴_销控明细表.xlsx
@@ -205,61 +205,61 @@
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -755,6 +779,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -805,6 +849,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -855,6 +919,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -905,6 +989,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -955,6 +1059,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1005,6 +1129,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1055,6 +1199,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1090,7 +1254,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2014-09-21</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1101,6 +1265,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5685000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>20598</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1136,7 +1316,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2014-10-08</t>
+          <t>2014-10-09</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1147,6 +1327,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5547000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>20469</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1182,7 +1378,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2014-09-11</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1193,6 +1389,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7824000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>18028</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1239,6 +1451,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>9795240</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>18587</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1274,7 +1502,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1285,6 +1513,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5670000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>20543</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1320,7 +1564,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1331,6 +1575,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5533000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>20417</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1366,7 +1626,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1377,6 +1637,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7805000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>17984</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1423,6 +1699,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>9602320</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>18221</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1458,7 +1750,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2014-10-02</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1469,6 +1761,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5559000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>20141</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1504,7 +1812,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2014-10-02</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1515,6 +1823,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>5423000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>20011</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1550,7 +1874,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1561,6 +1885,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>7460000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>17189</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1607,6 +1947,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>9505860</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>18038</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1642,7 +1998,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2014-10-07</t>
+          <t>2014-10-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1653,6 +2009,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>5503000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>20011</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1688,7 +2060,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1699,6 +2071,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>5369000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>19812</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1734,7 +2122,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2014-12-09</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1745,6 +2133,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>7421000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>17099</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1791,6 +2195,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>9412130</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>17860</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1826,7 +2246,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2014-10-05</t>
+          <t>2014-10-06</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1837,6 +2257,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>5448000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>19739</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1872,7 +2308,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1883,6 +2319,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5316000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>19401</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1929,6 +2381,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>7353710</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>17062</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1975,6 +2443,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>9319310</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>17684</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2010,7 +2494,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2021,6 +2505,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5367000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>19446</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2056,7 +2556,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2067,6 +2567,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5294000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>19321</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2102,7 +2618,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2014-12-17</t>
+          <t>2014-12-18</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2113,6 +2629,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>7229000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>16773</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2159,6 +2691,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9227400</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>17509</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2194,7 +2742,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2205,6 +2753,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>5313000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>19320</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2240,7 +2804,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-08-10</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2251,6 +2815,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>5241000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>19128</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2286,7 +2866,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
+          <t>2014-10-22</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2297,6 +2877,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7158000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>16608</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2343,6 +2939,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>9136400</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>17337</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2378,7 +2990,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2014-09-04</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2389,6 +3001,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5261000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>19062</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2424,7 +3052,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2014-09-03</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2435,6 +3063,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5189000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>18938</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2470,7 +3114,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2014-10-02</t>
+          <t>2014-10-03</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2481,6 +3125,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7087000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>16443</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2527,6 +3187,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>9045400</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>17164</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2562,7 +3238,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2014-08-25</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2573,6 +3249,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5208000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>18870</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2608,7 +3300,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2619,6 +3311,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5138000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>18752</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2654,7 +3362,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2014-10-26</t>
+          <t>2014-10-27</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2665,6 +3373,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>7013000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>16271</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2711,6 +3435,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>8737820</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>16580</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2746,7 +3486,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2757,6 +3497,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>4904000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>17768</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2792,7 +3548,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2014-08-24</t>
+          <t>2014-08-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2803,6 +3559,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>4886000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>17832</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2838,7 +3610,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2014-08-26</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2849,6 +3621,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>6742000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>15643</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2895,6 +3683,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>8737820</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>16580</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2930,7 +3734,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2941,6 +3745,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4904000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>17768</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2976,7 +3796,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2014-08-26</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2987,6 +3807,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>4886000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>17832</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3022,7 +3858,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3033,6 +3869,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>6742000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>15643</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3079,6 +3931,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8651370</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>16416</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3114,7 +3982,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3125,6 +3993,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>4855000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>17655</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3160,7 +4044,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2014-08-24</t>
+          <t>2014-08-25</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3171,6 +4055,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>4837000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>17653</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3206,7 +4106,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3217,6 +4117,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>6674000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>15485</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3263,6 +4179,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>8607690</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>16333</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3298,7 +4230,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3309,6 +4241,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>4831000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>17504</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3344,7 +4292,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3355,6 +4303,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>4813000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>17566</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3390,7 +4354,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3401,6 +4365,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>6496000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>15072</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3447,6 +4427,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>8847280</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>16788</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3482,7 +4478,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3493,6 +4489,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>4807000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>17417</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3528,7 +4540,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3539,6 +4551,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>4789000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>17478</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3574,7 +4602,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3585,6 +4613,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>6609000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>15334</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3631,6 +4675,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>8804040</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>16706</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3666,7 +4726,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3677,6 +4737,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>4783000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>17330</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3712,7 +4788,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3723,6 +4799,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>4766000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>17394</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3758,7 +4850,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3769,6 +4861,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>6575000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>15255</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3815,6 +4923,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>8759860</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>16622</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3850,7 +4974,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3861,6 +4985,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>4759000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>17243</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3896,7 +5036,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2014-08-26</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3907,6 +5047,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>4742000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>17307</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3942,7 +5098,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3953,6 +5109,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>6542000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>15179</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3999,6 +5171,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>8630140</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>16376</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4034,7 +5222,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2014-08-26</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4045,6 +5233,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>4859000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>17605</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4080,7 +5284,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4091,6 +5295,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>4793000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>17493</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4126,7 +5346,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2014-08-18</t>
+          <t>2014-08-19</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4137,6 +5357,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>6510000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>15104</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4183,6 +5419,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>8586900</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>16294</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4218,7 +5470,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2014-09-04</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4229,6 +5481,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>4835000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>17518</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4264,7 +5532,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2014-08-26</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4275,6 +5543,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>4770000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>17409</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4310,7 +5594,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4321,6 +5605,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>6478000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>15030</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4367,6 +5667,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>8586900</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>16294</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4402,7 +5718,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4413,6 +5729,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>4958000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>17964</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4448,7 +5780,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4459,6 +5791,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>4890000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>17847</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4494,7 +5842,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4505,6 +5853,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>6478000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>15030</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4551,6 +5915,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>8502300</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>16133</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4586,7 +5966,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4597,6 +5977,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>4787000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>17344</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4632,7 +6028,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4643,6 +6039,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>4722000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>17234</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4678,7 +6090,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-03</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4689,6 +6101,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>6414000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>14882</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4735,6 +6163,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7950670</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>15087</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4770,7 +6214,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4781,6 +6225,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>4625000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>16757</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4816,7 +6276,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2014-08-09</t>
+          <t>2014-08-10</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4827,6 +6287,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>4629000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>16894</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4862,7 +6338,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4873,6 +6349,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>6287000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>14587</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4919,6 +6411,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>7681310</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>14576</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>90天付款計劃</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4954,7 +6462,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2014-08-24</t>
+          <t>2014-08-25</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4965,6 +6473,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>4354000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>15775</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5000,7 +6524,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5011,6 +6535,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>4538000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>16562</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5046,7 +6586,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5057,6 +6597,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>6164000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>14302</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5092,7 +6648,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5103,6 +6659,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>8118000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>16567</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5138,7 +6710,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5149,6 +6721,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>4623000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18201</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5184,7 +6772,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2014-09-04</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5195,6 +6783,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>4997000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>19751</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5245,13 +6849,33 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5447,7 +7071,7 @@
           <t>A | 434呎 (1房)
 $782万
 $18,028/呎
-(14年-09月-10日)</t>
+(14年-09月-11日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5455,7 +7079,7 @@
           <t>B | 271呎 (1房)
 $555万
 $20,469/呎
-(14年-10月-08日)</t>
+(14年-10月-09日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -5463,7 +7087,7 @@
           <t>C | 276呎 (1房)
 $568万
 $20,598/呎
-(14年-09月-21日)</t>
+(14年-09月-22日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -5486,7 +7110,7 @@
           <t>A | 434呎 (1房)
 $780万
 $17,984/呎
-(14年-09月-18日)</t>
+(14年-09月-19日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5494,7 +7118,7 @@
           <t>B | 271呎 (1房)
 $553万
 $20,417/呎
-(14年-09月-07日)</t>
+(14年-09月-08日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -5502,7 +7126,7 @@
           <t>C | 276呎 (1房)
 $567万
 $20,543/呎
-(14年-09月-02日)</t>
+(14年-09月-03日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -5525,7 +7149,7 @@
           <t>A | 434呎 (1房)
 $746万
 $17,189/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5533,7 +7157,7 @@
           <t>B | 271呎 (1房)
 $542万
 $20,011/呎
-(14年-10月-02日)</t>
+(14年-10月-03日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -5541,7 +7165,7 @@
           <t>C | 276呎 (1房)
 $556万
 $20,141/呎
-(14年-10月-02日)</t>
+(14年-10月-03日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -5564,7 +7188,7 @@
           <t>A | 434呎 (1房)
 $742万
 $17,099/呎
-(14年-12月-09日)</t>
+(14年-12月-10日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -5572,7 +7196,7 @@
           <t>B | 271呎 (1房)
 $537万
 $19,812/呎
-(14年-09月-07日)</t>
+(14年-09月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -5580,7 +7204,7 @@
           <t>C | 275呎 (1房)
 $550万
 $20,011/呎
-(14年-10月-07日)</t>
+(14年-10月-08日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -5611,7 +7235,7 @@
           <t>B | 274呎 (1房)
 $532万
 $19,401/呎
-(14年-09月-07日)</t>
+(14年-09月-08日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -5619,7 +7243,7 @@
           <t>C | 276呎 (1房)
 $545万
 $19,739/呎
-(14年-10月-05日)</t>
+(14年-10月-06日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5642,7 +7266,7 @@
           <t>A | 431呎 (1房)
 $723万
 $16,773/呎
-(14年-12月-17日)</t>
+(14年-12月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5650,7 +7274,7 @@
           <t>B | 274呎 (1房)
 $529万
 $19,321/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -5658,7 +7282,7 @@
           <t>C | 276呎 (1房)
 $537万
 $19,446/呎
-(14年-08月-31日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -5681,7 +7305,7 @@
           <t>A | 431呎 (1房)
 $716万
 $16,608/呎
-(14年-10月-21日)</t>
+(14年-10月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5689,7 +7313,7 @@
           <t>B | 274呎 (1房)
 $524万
 $19,128/呎
-(14年-08月-09日)</t>
+(14年-08月-10日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -5697,7 +7321,7 @@
           <t>C | 275呎 (1房)
 $531万
 $19,320/呎
-(14年-08月-31日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5720,7 +7344,7 @@
           <t>A | 431呎 (1房)
 $709万
 $16,443/呎
-(14年-10月-02日)</t>
+(14年-10月-03日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5728,7 +7352,7 @@
           <t>B | 274呎 (1房)
 $519万
 $18,938/呎
-(14年-09月-03日)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5736,7 +7360,7 @@
           <t>C | 276呎 (1房)
 $526万
 $19,062/呎
-(14年-09月-04日)</t>
+(14年-09月-05日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -5759,7 +7383,7 @@
           <t>A | 431呎 (1房)
 $701万
 $16,271/呎
-(14年-10月-26日)</t>
+(14年-10月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5767,7 +7391,7 @@
           <t>B | 274呎 (1房)
 $514万
 $18,752/呎
-(14年-08月-31日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5775,7 +7399,7 @@
           <t>C | 276呎 (1房)
 $521万
 $18,870/呎
-(14年-08月-25日)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -5798,7 +7422,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(14年-08月-26日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5806,7 +7430,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(14年-08月-24日)</t>
+(14年-08月-25日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5814,7 +7438,7 @@
           <t>C | 276呎 (1房)
 $490万
 $17,768/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -5837,7 +7461,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5845,7 +7469,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(14年-08月-26日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5853,7 +7477,7 @@
           <t>C | 276呎 (1房)
 $490万
 $17,768/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -5876,7 +7500,7 @@
           <t>A | 431呎 (1房)
 $667万
 $15,485/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5884,7 +7508,7 @@
           <t>B | 274呎 (1房)
 $484万
 $17,653/呎
-(14年-08月-24日)</t>
+(14年-08月-25日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5892,7 +7516,7 @@
           <t>C | 275呎 (1房)
 $486万
 $17,655/呎
-(14年-08月-18日)</t>
+(14年-08月-19日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -5915,7 +7539,7 @@
           <t>A | 431呎 (1房)
 $650万
 $15,072/呎
-(14年-09月-09日)</t>
+(14年-09月-10日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5923,7 +7547,7 @@
           <t>B | 274呎 (1房)
 $481万
 $17,566/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5931,7 +7555,7 @@
           <t>C | 276呎 (1房)
 $483万
 $17,504/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -5954,7 +7578,7 @@
           <t>A | 431呎 (1房)
 $661万
 $15,334/呎
-(14年-09月-07日)</t>
+(14年-09月-08日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5962,7 +7586,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,478/呎
-(14年-08月-27日)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5970,7 +7594,7 @@
           <t>C | 276呎 (1房)
 $481万
 $17,417/呎
-(14年-08月-28日)</t>
+(14年-08月-29日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -5993,7 +7617,7 @@
           <t>A | 431呎 (1房)
 $658万
 $15,255/呎
-(14年-08月-27日)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -6001,7 +7625,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,394/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -6009,7 +7633,7 @@
           <t>C | 276呎 (1房)
 $478万
 $17,330/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -6032,7 +7656,7 @@
           <t>A | 431呎 (1房)
 $654万
 $15,179/呎
-(14年-09月-09日)</t>
+(14年-09月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -6040,7 +7664,7 @@
           <t>B | 274呎 (1房)
 $474万
 $17,307/呎
-(14年-08月-26日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -6048,7 +7672,7 @@
           <t>C | 276呎 (1房)
 $476万
 $17,243/呎
-(14年-08月-18日)</t>
+(14年-08月-19日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -6071,7 +7695,7 @@
           <t>A | 431呎 (1房)
 $651万
 $15,104/呎
-(14年-08月-18日)</t>
+(14年-08月-19日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -6079,7 +7703,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,493/呎
-(14年-08月-28日)</t>
+(14年-08月-29日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -6087,7 +7711,7 @@
           <t>C | 276呎 (1房)
 $486万
 $17,605/呎
-(14年-08月-26日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -6110,7 +7734,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -6118,7 +7742,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,409/呎
-(14年-08月-26日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -6126,7 +7750,7 @@
           <t>C | 276呎 (1房)
 $484万
 $17,518/呎
-(14年-09月-04日)</t>
+(14年-09月-05日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -6149,7 +7773,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(14年-08月-27日)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -6157,7 +7781,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,847/呎
-(14年-09月-07日)</t>
+(14年-09月-08日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -6165,7 +7789,7 @@
           <t>C | 276呎 (1房)
 $496万
 $17,964/呎
-(14年-09月-07日)</t>
+(14年-09月-08日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -6188,7 +7812,7 @@
           <t>A | 431呎 (1房)
 $641万
 $14,882/呎
-(14年-08月-02日)</t>
+(14年-08月-03日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -6196,7 +7820,7 @@
           <t>B | 274呎 (1房)
 $472万
 $17,234/呎
-(14年-08月-27日)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -6204,7 +7828,7 @@
           <t>C | 276呎 (1房)
 $479万
 $17,344/呎
-(14年-08月-31日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -6227,7 +7851,7 @@
           <t>A | 431呎 (1房)
 $629万
 $14,587/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -6235,7 +7859,7 @@
           <t>B | 274呎 (1房)
 $463万
 $16,894/呎
-(14年-08月-09日)</t>
+(14年-08月-10日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -6243,7 +7867,7 @@
           <t>C | 276呎 (1房)
 $462万
 $16,757/呎
-(14年-08月-31日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -6266,7 +7890,7 @@
           <t>A | 431呎 (1房)
 $616万
 $14,302/呎
-(14年-09月-02日)</t>
+(14年-09月-03日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -6274,7 +7898,7 @@
           <t>B | 274呎 (1房)
 $454万
 $16,562/呎
-(14年-09月-01日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -6282,7 +7906,7 @@
           <t>C | 276呎 (1房)
 $435万
 $15,775/呎
-(14年-08月-24日)</t>
+(14年-08月-25日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -6313,7 +7937,7 @@
           <t>B | 253呎 (1房)
 $500万
 $19,751/呎
-(14年-09月-04日)</t>
+(14年-09月-05日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6321,7 +7945,7 @@
           <t>C | 254呎 (1房)
 $462万
 $18,201/呎
-(14年-08月-01日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -6329,7 +7953,7 @@
           <t>D | 490呎 (2房)
 $812万
 $16,567/呎
-(14年-08月-31日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
     </row>

--- a/港岛-筲箕湾-远晴/远晴_销控明细表.xlsx
+++ b/港岛-筲箕湾-远晴/远晴_销控明细表.xlsx
@@ -205,61 +205,61 @@
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -648,10 +648,6 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -709,26 +705,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>最高折扣</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>折实总价 (港币)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>折实呎价 (港币/呎)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>付款办法</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -779,26 +755,6 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -849,26 +805,6 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -919,26 +855,6 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -989,26 +905,6 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1059,26 +955,6 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1129,26 +1005,6 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1199,26 +1055,6 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1254,7 +1090,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2014-09-22</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1265,22 +1101,6 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>5685000</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>20598</v>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1316,7 +1136,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2014-10-09</t>
+          <t>2014-10-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1327,22 +1147,6 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>5547000</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>20469</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1378,7 +1182,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1389,22 +1193,6 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>7824000</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>18028</v>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1451,22 +1239,6 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>9795240</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>18587</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1502,7 +1274,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2014-09-03</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1513,22 +1285,6 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>5670000</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>20543</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1564,7 +1320,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1575,22 +1331,6 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>5533000</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>20417</v>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1626,7 +1366,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2014-09-18</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1637,22 +1377,6 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>7805000</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>17984</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1699,22 +1423,6 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>9602320</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>18221</v>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1750,7 +1458,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1761,22 +1469,6 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>5559000</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>20141</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1812,7 +1504,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1823,22 +1515,6 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>5423000</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>20011</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1874,7 +1550,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1885,22 +1561,6 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>7460000</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>17189</v>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1947,22 +1607,6 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>9505860</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>18038</v>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1998,7 +1642,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2014-10-08</t>
+          <t>2014-10-07</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2009,22 +1653,6 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>5503000</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>20011</v>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2060,7 +1688,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2071,22 +1699,6 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>5369000</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>19812</v>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2122,7 +1734,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2014-12-10</t>
+          <t>2014-12-09</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2133,22 +1745,6 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>7421000</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>17099</v>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2195,22 +1791,6 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>9412130</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>17860</v>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2246,7 +1826,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2014-10-06</t>
+          <t>2014-10-05</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2257,22 +1837,6 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>5448000</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>19739</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2308,7 +1872,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2319,22 +1883,6 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>5316000</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>19401</v>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2381,22 +1929,6 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>7353710</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>17062</v>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2443,22 +1975,6 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>9319310</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>17684</v>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2494,7 +2010,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2505,22 +2021,6 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>5367000</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>19446</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2556,7 +2056,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2567,22 +2067,6 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>5294000</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>19321</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2618,7 +2102,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2014-12-18</t>
+          <t>2014-12-17</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2629,22 +2113,6 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>7229000</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>16773</v>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2691,22 +2159,6 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>9227400</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>17509</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2742,7 +2194,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2753,22 +2205,6 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>5313000</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>19320</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2804,7 +2240,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2014-08-10</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2815,22 +2251,6 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>5241000</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>19128</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2866,7 +2286,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2014-10-22</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2877,22 +2297,6 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>7158000</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>16608</v>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2939,22 +2343,6 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>9136400</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>17337</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -2990,7 +2378,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3001,22 +2389,6 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>5261000</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>19062</v>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3052,7 +2424,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2014-09-04</t>
+          <t>2014-09-03</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3063,22 +2435,6 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>5189000</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>18938</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3114,7 +2470,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2014-10-03</t>
+          <t>2014-10-02</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3125,22 +2481,6 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>7087000</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>16443</v>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3187,22 +2527,6 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>9045400</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>17164</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3238,7 +2562,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2014-08-26</t>
+          <t>2014-08-25</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3249,22 +2573,6 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>5208000</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>18870</v>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3300,7 +2608,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3311,22 +2619,6 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>5138000</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>18752</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3362,7 +2654,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2014-10-27</t>
+          <t>2014-10-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3373,22 +2665,6 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>7013000</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>16271</v>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3435,22 +2711,6 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>8737820</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>16580</v>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3486,7 +2746,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3497,22 +2757,6 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>4904000</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>17768</v>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3548,7 +2792,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2014-08-25</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3559,22 +2803,6 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>4886000</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>17832</v>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3610,7 +2838,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3621,22 +2849,6 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>6742000</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>15643</v>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3683,22 +2895,6 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>8737820</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>16580</v>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3734,7 +2930,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3745,22 +2941,6 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>4904000</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>17768</v>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3796,7 +2976,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3807,22 +2987,6 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>4886000</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>17832</v>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3858,7 +3022,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3869,22 +3033,6 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>6742000</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>15643</v>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3931,22 +3079,6 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>8651370</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>16416</v>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -3982,7 +3114,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3993,22 +3125,6 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>4855000</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>17655</v>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4044,7 +3160,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2014-08-25</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4055,22 +3171,6 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>4837000</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>17653</v>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4106,7 +3206,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4117,22 +3217,6 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>6674000</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>15485</v>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4179,22 +3263,6 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>8607690</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>16333</v>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4230,7 +3298,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4241,22 +3309,6 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>4831000</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>17504</v>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4292,7 +3344,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4303,22 +3355,6 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>4813000</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>17566</v>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4354,7 +3390,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4365,22 +3401,6 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>6496000</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>15072</v>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4427,22 +3447,6 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>8847280</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>16788</v>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4478,7 +3482,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4489,22 +3493,6 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>4807000</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>17417</v>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4540,7 +3528,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4551,22 +3539,6 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>4789000</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>17478</v>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4602,7 +3574,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4613,22 +3585,6 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>6609000</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>15334</v>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4675,22 +3631,6 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>8804040</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>16706</v>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4726,7 +3666,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4737,22 +3677,6 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>4783000</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>17330</v>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4788,7 +3712,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4799,22 +3723,6 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>4766000</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>17394</v>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4850,7 +3758,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4861,22 +3769,6 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>6575000</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>15255</v>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4923,22 +3815,6 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>8759860</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>16622</v>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -4974,7 +3850,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4985,22 +3861,6 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>4759000</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>17243</v>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5036,7 +3896,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5047,22 +3907,6 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>4742000</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>17307</v>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N71" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5098,7 +3942,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5109,22 +3953,6 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>6542000</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>15179</v>
-      </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5171,22 +3999,6 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>8630140</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>16376</v>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5222,7 +4034,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5233,22 +4045,6 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>4859000</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>17605</v>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5284,7 +4080,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5295,22 +4091,6 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>4793000</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>17493</v>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5346,7 +4126,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2014-08-19</t>
+          <t>2014-08-18</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5357,22 +4137,6 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>6510000</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>15104</v>
-      </c>
-      <c r="M76" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N76" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5419,22 +4183,6 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>8586900</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>16294</v>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N77" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5470,7 +4218,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5481,22 +4229,6 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>4835000</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>17518</v>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N78" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5532,7 +4264,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2014-08-27</t>
+          <t>2014-08-26</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5543,22 +4275,6 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>4770000</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>17409</v>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5594,7 +4310,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5605,22 +4321,6 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>6478000</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>15030</v>
-      </c>
-      <c r="M80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5667,22 +4367,6 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>8586900</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>16294</v>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N81" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5718,7 +4402,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5729,22 +4413,6 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>4958000</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>17964</v>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5780,7 +4448,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5791,22 +4459,6 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>4890000</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>17847</v>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5842,7 +4494,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5853,22 +4505,6 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>6478000</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>15030</v>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5915,22 +4551,6 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>8502300</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>16133</v>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N85" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -5966,7 +4586,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5977,22 +4597,6 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>4787000</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>17344</v>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6028,7 +4632,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2014-08-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6039,22 +4643,6 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>4722000</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>17234</v>
-      </c>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6090,7 +4678,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2014-08-03</t>
+          <t>2014-08-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6101,22 +4689,6 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>6414000</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>14882</v>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6163,22 +4735,6 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>7950670</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>15087</v>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6214,7 +4770,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6225,22 +4781,6 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>4625000</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>16757</v>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6276,7 +4816,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2014-08-10</t>
+          <t>2014-08-09</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6287,22 +4827,6 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>4629000</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>16894</v>
-      </c>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6338,7 +4862,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6349,22 +4873,6 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>6287000</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>14587</v>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6411,22 +4919,6 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>7681310</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>14576</v>
-      </c>
-      <c r="M93" s="3" t="inlineStr">
-        <is>
-          <t>90天付款計劃</t>
-        </is>
-      </c>
-      <c r="N93" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6462,7 +4954,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2014-08-25</t>
+          <t>2014-08-24</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6473,22 +4965,6 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>4354000</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>15775</v>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6524,7 +5000,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2014-09-02</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6535,22 +5011,6 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>4538000</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>16562</v>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6586,7 +5046,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2014-09-03</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6597,22 +5057,6 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>6164000</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>14302</v>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6648,7 +5092,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6659,22 +5103,6 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="n">
-        <v>8118000</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>16567</v>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6710,7 +5138,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2014-08-02</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6721,22 +5149,6 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="n">
-        <v>4623000</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>18201</v>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6772,7 +5184,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2014-09-04</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6783,22 +5195,6 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="n">
-        <v>4997000</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>19751</v>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -6849,33 +5245,13 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -7071,7 +5447,7 @@
           <t>A | 434呎 (1房)
 $782万
 $18,028/呎
-(14年-09月-11日)</t>
+(14年-09月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -7079,7 +5455,7 @@
           <t>B | 271呎 (1房)
 $555万
 $20,469/呎
-(14年-10月-09日)</t>
+(14年-10月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -7087,7 +5463,7 @@
           <t>C | 276呎 (1房)
 $568万
 $20,598/呎
-(14年-09月-22日)</t>
+(14年-09月-21日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -7110,7 +5486,7 @@
           <t>A | 434呎 (1房)
 $780万
 $17,984/呎
-(14年-09月-19日)</t>
+(14年-09月-18日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -7118,7 +5494,7 @@
           <t>B | 271呎 (1房)
 $553万
 $20,417/呎
-(14年-09月-08日)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -7126,7 +5502,7 @@
           <t>C | 276呎 (1房)
 $567万
 $20,543/呎
-(14年-09月-03日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -7149,7 +5525,7 @@
           <t>A | 434呎 (1房)
 $746万
 $17,189/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7157,7 +5533,7 @@
           <t>B | 271呎 (1房)
 $542万
 $20,011/呎
-(14年-10月-03日)</t>
+(14年-10月-02日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -7165,7 +5541,7 @@
           <t>C | 276呎 (1房)
 $556万
 $20,141/呎
-(14年-10月-03日)</t>
+(14年-10月-02日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -7188,7 +5564,7 @@
           <t>A | 434呎 (1房)
 $742万
 $17,099/呎
-(14年-12月-10日)</t>
+(14年-12月-09日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7196,7 +5572,7 @@
           <t>B | 271呎 (1房)
 $537万
 $19,812/呎
-(14年-09月-08日)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -7204,7 +5580,7 @@
           <t>C | 275呎 (1房)
 $550万
 $20,011/呎
-(14年-10月-08日)</t>
+(14年-10月-07日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -7235,7 +5611,7 @@
           <t>B | 274呎 (1房)
 $532万
 $19,401/呎
-(14年-09月-08日)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -7243,7 +5619,7 @@
           <t>C | 276呎 (1房)
 $545万
 $19,739/呎
-(14年-10月-06日)</t>
+(14年-10月-05日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7266,7 +5642,7 @@
           <t>A | 431呎 (1房)
 $723万
 $16,773/呎
-(14年-12月-18日)</t>
+(14年-12月-17日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7274,7 +5650,7 @@
           <t>B | 274呎 (1房)
 $529万
 $19,321/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -7282,7 +5658,7 @@
           <t>C | 276呎 (1房)
 $537万
 $19,446/呎
-(14年-09月-01日)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7305,7 +5681,7 @@
           <t>A | 431呎 (1房)
 $716万
 $16,608/呎
-(14年-10月-22日)</t>
+(14年-10月-21日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7313,7 +5689,7 @@
           <t>B | 274呎 (1房)
 $524万
 $19,128/呎
-(14年-08月-10日)</t>
+(14年-08月-09日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -7321,7 +5697,7 @@
           <t>C | 275呎 (1房)
 $531万
 $19,320/呎
-(14年-09月-01日)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7344,7 +5720,7 @@
           <t>A | 431呎 (1房)
 $709万
 $16,443/呎
-(14年-10月-03日)</t>
+(14年-10月-02日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7352,7 +5728,7 @@
           <t>B | 274呎 (1房)
 $519万
 $18,938/呎
-(14年-09月-04日)</t>
+(14年-09月-03日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7360,7 +5736,7 @@
           <t>C | 276呎 (1房)
 $526万
 $19,062/呎
-(14年-09月-05日)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -7383,7 +5759,7 @@
           <t>A | 431呎 (1房)
 $701万
 $16,271/呎
-(14年-10月-27日)</t>
+(14年-10月-26日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7391,7 +5767,7 @@
           <t>B | 274呎 (1房)
 $514万
 $18,752/呎
-(14年-09月-01日)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7399,7 +5775,7 @@
           <t>C | 276呎 (1房)
 $521万
 $18,870/呎
-(14年-08月-26日)</t>
+(14年-08月-25日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -7422,7 +5798,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(14年-08月-27日)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7430,7 +5806,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(14年-08月-25日)</t>
+(14年-08月-24日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -7438,7 +5814,7 @@
           <t>C | 276呎 (1房)
 $490万
 $17,768/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -7461,7 +5837,7 @@
           <t>A | 431呎 (1房)
 $674万
 $15,643/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7469,7 +5845,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,832/呎
-(14年-08月-27日)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -7477,7 +5853,7 @@
           <t>C | 276呎 (1房)
 $490万
 $17,768/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -7500,7 +5876,7 @@
           <t>A | 431呎 (1房)
 $667万
 $15,485/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7508,7 +5884,7 @@
           <t>B | 274呎 (1房)
 $484万
 $17,653/呎
-(14年-08月-25日)</t>
+(14年-08月-24日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7516,7 +5892,7 @@
           <t>C | 275呎 (1房)
 $486万
 $17,655/呎
-(14年-08月-19日)</t>
+(14年-08月-18日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7539,7 +5915,7 @@
           <t>A | 431呎 (1房)
 $650万
 $15,072/呎
-(14年-09月-10日)</t>
+(14年-09月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7547,7 +5923,7 @@
           <t>B | 274呎 (1房)
 $481万
 $17,566/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7555,7 +5931,7 @@
           <t>C | 276呎 (1房)
 $483万
 $17,504/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7578,7 +5954,7 @@
           <t>A | 431呎 (1房)
 $661万
 $15,334/呎
-(14年-09月-08日)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7586,7 +5962,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,478/呎
-(14年-08月-28日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7594,7 +5970,7 @@
           <t>C | 276呎 (1房)
 $481万
 $17,417/呎
-(14年-08月-29日)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -7617,7 +5993,7 @@
           <t>A | 431呎 (1房)
 $658万
 $15,255/呎
-(14年-08月-28日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7625,7 +6001,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,394/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7633,7 +6009,7 @@
           <t>C | 276呎 (1房)
 $478万
 $17,330/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -7656,7 +6032,7 @@
           <t>A | 431呎 (1房)
 $654万
 $15,179/呎
-(14年-09月-10日)</t>
+(14年-09月-09日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7664,7 +6040,7 @@
           <t>B | 274呎 (1房)
 $474万
 $17,307/呎
-(14年-08月-27日)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7672,7 +6048,7 @@
           <t>C | 276呎 (1房)
 $476万
 $17,243/呎
-(14年-08月-19日)</t>
+(14年-08月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -7695,7 +6071,7 @@
           <t>A | 431呎 (1房)
 $651万
 $15,104/呎
-(14年-08月-19日)</t>
+(14年-08月-18日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -7703,7 +6079,7 @@
           <t>B | 274呎 (1房)
 $479万
 $17,493/呎
-(14年-08月-29日)</t>
+(14年-08月-28日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -7711,7 +6087,7 @@
           <t>C | 276呎 (1房)
 $486万
 $17,605/呎
-(14年-08月-27日)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -7734,7 +6110,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7742,7 +6118,7 @@
           <t>B | 274呎 (1房)
 $477万
 $17,409/呎
-(14年-08月-27日)</t>
+(14年-08月-26日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -7750,7 +6126,7 @@
           <t>C | 276呎 (1房)
 $484万
 $17,518/呎
-(14年-09月-05日)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -7773,7 +6149,7 @@
           <t>A | 431呎 (1房)
 $648万
 $15,030/呎
-(14年-08月-28日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7781,7 +6157,7 @@
           <t>B | 274呎 (1房)
 $489万
 $17,847/呎
-(14年-09月-08日)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -7789,7 +6165,7 @@
           <t>C | 276呎 (1房)
 $496万
 $17,964/呎
-(14年-09月-08日)</t>
+(14年-09月-07日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -7812,7 +6188,7 @@
           <t>A | 431呎 (1房)
 $641万
 $14,882/呎
-(14年-08月-03日)</t>
+(14年-08月-02日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -7820,7 +6196,7 @@
           <t>B | 274呎 (1房)
 $472万
 $17,234/呎
-(14年-08月-28日)</t>
+(14年-08月-27日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -7828,7 +6204,7 @@
           <t>C | 276呎 (1房)
 $479万
 $17,344/呎
-(14年-09月-01日)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -7851,7 +6227,7 @@
           <t>A | 431呎 (1房)
 $629万
 $14,587/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -7859,7 +6235,7 @@
           <t>B | 274呎 (1房)
 $463万
 $16,894/呎
-(14年-08月-10日)</t>
+(14年-08月-09日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -7867,7 +6243,7 @@
           <t>C | 276呎 (1房)
 $462万
 $16,757/呎
-(14年-09月-01日)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -7890,7 +6266,7 @@
           <t>A | 431呎 (1房)
 $616万
 $14,302/呎
-(14年-09月-03日)</t>
+(14年-09月-02日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -7898,7 +6274,7 @@
           <t>B | 274呎 (1房)
 $454万
 $16,562/呎
-(14年-09月-02日)</t>
+(14年-09月-01日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -7906,7 +6282,7 @@
           <t>C | 276呎 (1房)
 $435万
 $15,775/呎
-(14年-08月-25日)</t>
+(14年-08月-24日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -7937,7 +6313,7 @@
           <t>B | 253呎 (1房)
 $500万
 $19,751/呎
-(14年-09月-05日)</t>
+(14年-09月-04日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -7945,7 +6321,7 @@
           <t>C | 254呎 (1房)
 $462万
 $18,201/呎
-(14年-08月-02日)</t>
+(14年-08月-01日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -7953,7 +6329,7 @@
           <t>D | 490呎 (2房)
 $812万
 $16,567/呎
-(14年-09月-01日)</t>
+(14年-08月-31日)</t>
         </is>
       </c>
     </row>
